--- a/tool/PMP/old/conventional_cesarcolombia_1959_2009.xlsx
+++ b/tool/PMP/old/conventional_cesarcolombia_1959_2009.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HydroTools\tool\PMP\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050E1CD1-5E83-4578-82C7-0A56E185717E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD5632CF-5CDF-4430-847B-0E1A2A237014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{AEC9431B-F4C3-4A0D-893F-F4F358360E67}"/>
   </bookViews>
@@ -579,6 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7C4D4F-C4DE-4983-AADE-B1C1D9129ECF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D766"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
@@ -603,7 +604,7 @@
         <v>Station,Date,Value</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A2" s="1">
         <v>25020230</v>
       </c>
@@ -615,7 +616,7 @@
         <v>25020230,1959,</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A3" s="1">
         <v>25020230</v>
       </c>
@@ -627,7 +628,7 @@
         <v>25020230,1960,</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A4" s="1">
         <v>25020230</v>
       </c>
@@ -639,7 +640,7 @@
         <v>25020230,1961,</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A5" s="1">
         <v>25020230</v>
       </c>
@@ -651,7 +652,7 @@
         <v>25020230,1962,</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A6" s="1">
         <v>25020230</v>
       </c>
@@ -663,7 +664,7 @@
         <v>25020230,1963,</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A7" s="1">
         <v>25020230</v>
       </c>
@@ -675,7 +676,7 @@
         <v>25020230,1964,</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A8" s="1">
         <v>25020230</v>
       </c>
@@ -687,7 +688,7 @@
         <v>25020230,1965,</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A9" s="1">
         <v>25020230</v>
       </c>
@@ -699,7 +700,7 @@
         <v>25020230,1966,</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A10" s="1">
         <v>25020230</v>
       </c>
@@ -711,7 +712,7 @@
         <v>25020230,1967,</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A11" s="1">
         <v>25020230</v>
       </c>
@@ -723,7 +724,7 @@
         <v>25020230,1968,</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A12" s="1">
         <v>25020230</v>
       </c>
@@ -738,7 +739,7 @@
         <v>25020230,1969,82</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A13" s="1">
         <v>25020230</v>
       </c>
@@ -753,7 +754,7 @@
         <v>25020230,1970,82</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A14" s="1">
         <v>25020230</v>
       </c>
@@ -768,7 +769,7 @@
         <v>25020230,1971,125</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A15" s="1">
         <v>25020230</v>
       </c>
@@ -783,7 +784,7 @@
         <v>25020230,1972,80</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A16" s="1">
         <v>25020230</v>
       </c>
@@ -798,7 +799,7 @@
         <v>25020230,1973,130</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A17" s="1">
         <v>25020230</v>
       </c>
@@ -813,7 +814,7 @@
         <v>25020230,1974,135</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A18" s="1">
         <v>25020230</v>
       </c>
@@ -828,7 +829,7 @@
         <v>25020230,1975,139</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A19" s="1">
         <v>25020230</v>
       </c>
@@ -843,7 +844,7 @@
         <v>25020230,1976,80</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A20" s="1">
         <v>25020230</v>
       </c>
@@ -858,7 +859,7 @@
         <v>25020230,1977,135</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A21" s="1">
         <v>25020230</v>
       </c>
@@ -873,7 +874,7 @@
         <v>25020230,1978,142</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A22" s="1">
         <v>25020230</v>
       </c>
@@ -888,7 +889,7 @@
         <v>25020230,1979,151</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A23" s="1">
         <v>25020230</v>
       </c>
@@ -903,7 +904,7 @@
         <v>25020230,1980,108</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A24" s="1">
         <v>25020230</v>
       </c>
@@ -918,7 +919,7 @@
         <v>25020230,1981,150</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A25" s="1">
         <v>25020230</v>
       </c>
@@ -933,7 +934,7 @@
         <v>25020230,1982,148</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A26" s="1">
         <v>25020230</v>
       </c>
@@ -948,7 +949,7 @@
         <v>25020230,1983,120</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A27" s="1">
         <v>25020230</v>
       </c>
@@ -963,7 +964,7 @@
         <v>25020230,1984,155</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A28" s="1">
         <v>25020230</v>
       </c>
@@ -978,7 +979,7 @@
         <v>25020230,1985,122</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A29" s="1">
         <v>25020230</v>
       </c>
@@ -993,7 +994,7 @@
         <v>25020230,1986,136</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A30" s="1">
         <v>25020230</v>
       </c>
@@ -1008,7 +1009,7 @@
         <v>25020230,1987,46</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A31" s="1">
         <v>25020230</v>
       </c>
@@ -1023,7 +1024,7 @@
         <v>25020230,1988,95</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A32" s="1">
         <v>25020230</v>
       </c>
@@ -1038,7 +1039,7 @@
         <v>25020230,1989,85</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A33" s="1">
         <v>25020230</v>
       </c>
@@ -1053,7 +1054,7 @@
         <v>25020230,1990,89</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A34" s="1">
         <v>25020230</v>
       </c>
@@ -1068,7 +1069,7 @@
         <v>25020230,1991,65</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A35" s="1">
         <v>25020230</v>
       </c>
@@ -1083,7 +1084,7 @@
         <v>25020230,1992,62</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A36" s="1">
         <v>25020230</v>
       </c>
@@ -1098,7 +1099,7 @@
         <v>25020230,1993,90</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A37" s="1">
         <v>25020230</v>
       </c>
@@ -1113,7 +1114,7 @@
         <v>25020230,1994,135</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A38" s="1">
         <v>25020230</v>
       </c>
@@ -1128,7 +1129,7 @@
         <v>25020230,1995,90</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A39" s="1">
         <v>25020230</v>
       </c>
@@ -1143,7 +1144,7 @@
         <v>25020230,1996,41</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A40" s="1">
         <v>25020230</v>
       </c>
@@ -1158,7 +1159,7 @@
         <v>25020230,1997,85</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A41" s="1">
         <v>25020230</v>
       </c>
@@ -1173,7 +1174,7 @@
         <v>25020230,1998,71</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A42" s="1">
         <v>25020230</v>
       </c>
@@ -1188,7 +1189,7 @@
         <v>25020230,1999,110</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A43" s="1">
         <v>25020230</v>
       </c>
@@ -1203,7 +1204,7 @@
         <v>25020230,2000,122</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A44" s="1">
         <v>25020230</v>
       </c>
@@ -1218,7 +1219,7 @@
         <v>25020230,2001,134.5</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A45" s="1">
         <v>25020230</v>
       </c>
@@ -1233,7 +1234,7 @@
         <v>25020230,2002,109</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A46" s="1">
         <v>25020230</v>
       </c>
@@ -1248,7 +1249,7 @@
         <v>25020230,2003,80</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A47" s="1">
         <v>25020230</v>
       </c>
@@ -1263,7 +1264,7 @@
         <v>25020230,2004,80</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A48" s="1">
         <v>25020230</v>
       </c>
@@ -1278,7 +1279,7 @@
         <v>25020230,2005,40</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A49" s="1">
         <v>25020230</v>
       </c>
@@ -1293,7 +1294,7 @@
         <v>25020230,2006,90</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A50" s="1">
         <v>25020230</v>
       </c>
@@ -1308,7 +1309,7 @@
         <v>25020230,2007,150</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A51" s="1">
         <v>25020230</v>
       </c>
@@ -1323,7 +1324,7 @@
         <v>25020230,2008,160</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A52" s="1">
         <v>25020230</v>
       </c>
@@ -1338,7 +1339,7 @@
         <v>25020230,2009,150</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A53" s="1">
         <v>25020260</v>
       </c>
@@ -1350,7 +1351,7 @@
         <v>25020260,1959,</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A54" s="1">
         <v>25020260</v>
       </c>
@@ -1362,7 +1363,7 @@
         <v>25020260,1960,</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A55" s="1">
         <v>25020260</v>
       </c>
@@ -1374,7 +1375,7 @@
         <v>25020260,1961,</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A56" s="1">
         <v>25020260</v>
       </c>
@@ -1386,7 +1387,7 @@
         <v>25020260,1962,</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A57" s="1">
         <v>25020260</v>
       </c>
@@ -1398,7 +1399,7 @@
         <v>25020260,1963,</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A58" s="1">
         <v>25020260</v>
       </c>
@@ -1410,7 +1411,7 @@
         <v>25020260,1964,</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A59" s="1">
         <v>25020260</v>
       </c>
@@ -1422,7 +1423,7 @@
         <v>25020260,1965,</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A60" s="1">
         <v>25020260</v>
       </c>
@@ -1434,7 +1435,7 @@
         <v>25020260,1966,</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A61" s="1">
         <v>25020260</v>
       </c>
@@ -1446,7 +1447,7 @@
         <v>25020260,1967,</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A62" s="1">
         <v>25020260</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>25020260,1968,</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A63" s="1">
         <v>25020260</v>
       </c>
@@ -1473,7 +1474,7 @@
         <v>25020260,1969,112</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A64" s="1">
         <v>25020260</v>
       </c>
@@ -1488,7 +1489,7 @@
         <v>25020260,1970,100</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A65" s="1">
         <v>25020260</v>
       </c>
@@ -1503,7 +1504,7 @@
         <v>25020260,1971,85</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A66" s="1">
         <v>25020260</v>
       </c>
@@ -1518,7 +1519,7 @@
         <v>25020260,1972,72</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A67" s="1">
         <v>25020260</v>
       </c>
@@ -1533,7 +1534,7 @@
         <v>25020260,1973,128</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A68" s="1">
         <v>25020260</v>
       </c>
@@ -1548,7 +1549,7 @@
         <v>25020260,1974,155</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A69" s="1">
         <v>25020260</v>
       </c>
@@ -1563,7 +1564,7 @@
         <v>25020260,1975,172</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A70" s="1">
         <v>25020260</v>
       </c>
@@ -1578,7 +1579,7 @@
         <v>25020260,1976,123</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A71" s="1">
         <v>25020260</v>
       </c>
@@ -1593,7 +1594,7 @@
         <v>25020260,1977,115</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A72" s="1">
         <v>25020260</v>
       </c>
@@ -1608,7 +1609,7 @@
         <v>25020260,1978,170</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A73" s="1">
         <v>25020260</v>
       </c>
@@ -1623,7 +1624,7 @@
         <v>25020260,1979,136</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A74" s="1">
         <v>25020260</v>
       </c>
@@ -1638,7 +1639,7 @@
         <v>25020260,1980,105</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A75" s="1">
         <v>25020260</v>
       </c>
@@ -1653,7 +1654,7 @@
         <v>25020260,1981,100</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A76" s="1">
         <v>25020260</v>
       </c>
@@ -1668,7 +1669,7 @@
         <v>25020260,1982,80</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A77" s="1">
         <v>25020260</v>
       </c>
@@ -1683,7 +1684,7 @@
         <v>25020260,1983,149</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A78" s="1">
         <v>25020260</v>
       </c>
@@ -1698,7 +1699,7 @@
         <v>25020260,1984,145</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A79" s="1">
         <v>25020260</v>
       </c>
@@ -1713,7 +1714,7 @@
         <v>25020260,1985,110</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A80" s="1">
         <v>25020260</v>
       </c>
@@ -1728,7 +1729,7 @@
         <v>25020260,1986,52</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A81" s="1">
         <v>25020260</v>
       </c>
@@ -1743,7 +1744,7 @@
         <v>25020260,1987,170</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A82" s="1">
         <v>25020260</v>
       </c>
@@ -1758,7 +1759,7 @@
         <v>25020260,1988,105</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A83" s="1">
         <v>25020260</v>
       </c>
@@ -1773,7 +1774,7 @@
         <v>25020260,1989,115</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A84" s="1">
         <v>25020260</v>
       </c>
@@ -1788,7 +1789,7 @@
         <v>25020260,1990,63</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A85" s="1">
         <v>25020260</v>
       </c>
@@ -1803,7 +1804,7 @@
         <v>25020260,1991,130</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A86" s="1">
         <v>25020260</v>
       </c>
@@ -1818,7 +1819,7 @@
         <v>25020260,1992,147</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A87" s="1">
         <v>25020260</v>
       </c>
@@ -1833,7 +1834,7 @@
         <v>25020260,1993,78</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A88" s="1">
         <v>25020260</v>
       </c>
@@ -1848,7 +1849,7 @@
         <v>25020260,1994,84</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A89" s="1">
         <v>25020260</v>
       </c>
@@ -1863,7 +1864,7 @@
         <v>25020260,1995,98</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A90" s="1">
         <v>25020260</v>
       </c>
@@ -1878,7 +1879,7 @@
         <v>25020260,1996,106</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A91" s="1">
         <v>25020260</v>
       </c>
@@ -1893,7 +1894,7 @@
         <v>25020260,1997,74</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A92" s="1">
         <v>25020260</v>
       </c>
@@ -1908,7 +1909,7 @@
         <v>25020260,1998,98</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A93" s="1">
         <v>25020260</v>
       </c>
@@ -1923,7 +1924,7 @@
         <v>25020260,1999,152</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A94" s="1">
         <v>25020260</v>
       </c>
@@ -1938,7 +1939,7 @@
         <v>25020260,2000,97</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A95" s="1">
         <v>25020260</v>
       </c>
@@ -1953,7 +1954,7 @@
         <v>25020260,2001,97</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A96" s="1">
         <v>25020260</v>
       </c>
@@ -1968,7 +1969,7 @@
         <v>25020260,2002,93</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A97" s="1">
         <v>25020260</v>
       </c>
@@ -1983,7 +1984,7 @@
         <v>25020260,2003,93</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A98" s="1">
         <v>25020260</v>
       </c>
@@ -1998,7 +1999,7 @@
         <v>25020260,2004,112</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A99" s="1">
         <v>25020260</v>
       </c>
@@ -2013,7 +2014,7 @@
         <v>25020260,2005,75</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A100" s="1">
         <v>25020260</v>
       </c>
@@ -2028,7 +2029,7 @@
         <v>25020260,2006,137</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A101" s="1">
         <v>25020260</v>
       </c>
@@ -2043,7 +2044,7 @@
         <v>25020260,2007,149</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A102" s="1">
         <v>25020260</v>
       </c>
@@ -2058,7 +2059,7 @@
         <v>25020260,2008,138</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A103" s="1">
         <v>25020260</v>
       </c>
@@ -2073,7 +2074,7 @@
         <v>25020260,2009,107</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A104" s="1">
         <v>25020280</v>
       </c>
@@ -2085,7 +2086,7 @@
         <v>25020280,1959,</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A105" s="1">
         <v>25020280</v>
       </c>
@@ -2097,7 +2098,7 @@
         <v>25020280,1960,</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A106" s="1">
         <v>25020280</v>
       </c>
@@ -2109,7 +2110,7 @@
         <v>25020280,1961,</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A107" s="1">
         <v>25020280</v>
       </c>
@@ -2121,7 +2122,7 @@
         <v>25020280,1962,</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A108" s="1">
         <v>25020280</v>
       </c>
@@ -2133,7 +2134,7 @@
         <v>25020280,1963,</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A109" s="1">
         <v>25020280</v>
       </c>
@@ -2145,7 +2146,7 @@
         <v>25020280,1964,</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A110" s="1">
         <v>25020280</v>
       </c>
@@ -2157,7 +2158,7 @@
         <v>25020280,1965,</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A111" s="1">
         <v>25020280</v>
       </c>
@@ -2169,7 +2170,7 @@
         <v>25020280,1966,</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A112" s="1">
         <v>25020280</v>
       </c>
@@ -2181,7 +2182,7 @@
         <v>25020280,1967,</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A113" s="1">
         <v>25020280</v>
       </c>
@@ -2193,7 +2194,7 @@
         <v>25020280,1968,</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A114" s="1">
         <v>25020280</v>
       </c>
@@ -2208,7 +2209,7 @@
         <v>25020280,1969,132</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A115" s="1">
         <v>25020280</v>
       </c>
@@ -2223,7 +2224,7 @@
         <v>25020280,1970,115</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A116" s="1">
         <v>25020280</v>
       </c>
@@ -2238,7 +2239,7 @@
         <v>25020280,1971,100</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A117" s="1">
         <v>25020280</v>
       </c>
@@ -2253,7 +2254,7 @@
         <v>25020280,1972,97</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A118" s="1">
         <v>25020280</v>
       </c>
@@ -2268,7 +2269,7 @@
         <v>25020280,1973,116</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A119" s="1">
         <v>25020280</v>
       </c>
@@ -2283,7 +2284,7 @@
         <v>25020280,1974,92</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A120" s="1">
         <v>25020280</v>
       </c>
@@ -2298,7 +2299,7 @@
         <v>25020280,1975,104</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A121" s="1">
         <v>25020280</v>
       </c>
@@ -2313,7 +2314,7 @@
         <v>25020280,1976,82</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A122" s="1">
         <v>25020280</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>25020280,1977,90</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A123" s="1">
         <v>25020280</v>
       </c>
@@ -2343,7 +2344,7 @@
         <v>25020280,1978,130</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A124" s="1">
         <v>25020280</v>
       </c>
@@ -2358,7 +2359,7 @@
         <v>25020280,1979,116</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A125" s="1">
         <v>25020280</v>
       </c>
@@ -2373,7 +2374,7 @@
         <v>25020280,1980,130</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A126" s="1">
         <v>25020280</v>
       </c>
@@ -2388,7 +2389,7 @@
         <v>25020280,1981,78</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A127" s="1">
         <v>25020280</v>
       </c>
@@ -2403,7 +2404,7 @@
         <v>25020280,1982,150</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A128" s="1">
         <v>25020280</v>
       </c>
@@ -2418,7 +2419,7 @@
         <v>25020280,1983,103</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A129" s="1">
         <v>25020280</v>
       </c>
@@ -2433,7 +2434,7 @@
         <v>25020280,1984,150</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A130" s="1">
         <v>25020280</v>
       </c>
@@ -2448,7 +2449,7 @@
         <v>25020280,1985,98</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A131" s="1">
         <v>25020280</v>
       </c>
@@ -2463,7 +2464,7 @@
         <v>25020280,1986,55</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A132" s="1">
         <v>25020280</v>
       </c>
@@ -2478,7 +2479,7 @@
         <v>25020280,1987,90</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A133" s="1">
         <v>25020280</v>
       </c>
@@ -2493,7 +2494,7 @@
         <v>25020280,1988,88</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A134" s="1">
         <v>25020280</v>
       </c>
@@ -2508,7 +2509,7 @@
         <v>25020280,1989,77</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A135" s="1">
         <v>25020280</v>
       </c>
@@ -2523,7 +2524,7 @@
         <v>25020280,1990,92.6</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A136" s="1">
         <v>25020280</v>
       </c>
@@ -2538,7 +2539,7 @@
         <v>25020280,1991,90</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A137" s="1">
         <v>25020280</v>
       </c>
@@ -2553,7 +2554,7 @@
         <v>25020280,1992,105</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A138" s="1">
         <v>25020280</v>
       </c>
@@ -2568,7 +2569,7 @@
         <v>25020280,1993,120</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A139" s="1">
         <v>25020280</v>
       </c>
@@ -2583,7 +2584,7 @@
         <v>25020280,1994,100</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A140" s="1">
         <v>25020280</v>
       </c>
@@ -2598,7 +2599,7 @@
         <v>25020280,1995,70</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A141" s="1">
         <v>25020280</v>
       </c>
@@ -2613,7 +2614,7 @@
         <v>25020280,1996,150</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A142" s="1">
         <v>25020280</v>
       </c>
@@ -2628,7 +2629,7 @@
         <v>25020280,1997,70</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A143" s="1">
         <v>25020280</v>
       </c>
@@ -2643,7 +2644,7 @@
         <v>25020280,1998,124</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A144" s="1">
         <v>25020280</v>
       </c>
@@ -2658,7 +2659,7 @@
         <v>25020280,1999,130</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A145" s="1">
         <v>25020280</v>
       </c>
@@ -2673,7 +2674,7 @@
         <v>25020280,2000,120</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A146" s="1">
         <v>25020280</v>
       </c>
@@ -2688,7 +2689,7 @@
         <v>25020280,2001,70</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A147" s="1">
         <v>25020280</v>
       </c>
@@ -2703,7 +2704,7 @@
         <v>25020280,2002,96</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A148" s="1">
         <v>25020280</v>
       </c>
@@ -2718,7 +2719,7 @@
         <v>25020280,2003,271</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A149" s="1">
         <v>25020280</v>
       </c>
@@ -2733,7 +2734,7 @@
         <v>25020280,2004,90</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A150" s="1">
         <v>25020280</v>
       </c>
@@ -2748,7 +2749,7 @@
         <v>25020280,2005,106</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A151" s="1">
         <v>25020280</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>25020280,2006,125</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A152" s="1">
         <v>25020280</v>
       </c>
@@ -2778,7 +2779,7 @@
         <v>25020280,2007,90</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A153" s="1">
         <v>25020280</v>
       </c>
@@ -2793,7 +2794,7 @@
         <v>25020280,2008,121</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A154" s="1">
         <v>25020280</v>
       </c>
@@ -2808,7 +2809,7 @@
         <v>25020280,2009,90</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A155" s="1">
         <v>25020690</v>
       </c>
@@ -2820,7 +2821,7 @@
         <v>25020690,1959,</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A156" s="1">
         <v>25020690</v>
       </c>
@@ -2832,7 +2833,7 @@
         <v>25020690,1960,</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A157" s="1">
         <v>25020690</v>
       </c>
@@ -2844,7 +2845,7 @@
         <v>25020690,1961,</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A158" s="1">
         <v>25020690</v>
       </c>
@@ -2856,7 +2857,7 @@
         <v>25020690,1962,</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A159" s="1">
         <v>25020690</v>
       </c>
@@ -2868,7 +2869,7 @@
         <v>25020690,1963,</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A160" s="1">
         <v>25020690</v>
       </c>
@@ -2880,7 +2881,7 @@
         <v>25020690,1964,</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A161" s="1">
         <v>25020690</v>
       </c>
@@ -2892,7 +2893,7 @@
         <v>25020690,1965,</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A162" s="1">
         <v>25020690</v>
       </c>
@@ -2904,7 +2905,7 @@
         <v>25020690,1966,</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A163" s="1">
         <v>25020690</v>
       </c>
@@ -2916,7 +2917,7 @@
         <v>25020690,1967,</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A164" s="1">
         <v>25020690</v>
       </c>
@@ -2928,7 +2929,7 @@
         <v>25020690,1968,</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A165" s="1">
         <v>25020690</v>
       </c>
@@ -2940,7 +2941,7 @@
         <v>25020690,1969,</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A166" s="1">
         <v>25020690</v>
       </c>
@@ -2952,7 +2953,7 @@
         <v>25020690,1970,</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A167" s="1">
         <v>25020690</v>
       </c>
@@ -2964,7 +2965,7 @@
         <v>25020690,1971,</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A168" s="1">
         <v>25020690</v>
       </c>
@@ -2976,7 +2977,7 @@
         <v>25020690,1972,</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A169" s="1">
         <v>25020690</v>
       </c>
@@ -2991,7 +2992,7 @@
         <v>25020690,1973,113</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A170" s="1">
         <v>25020690</v>
       </c>
@@ -3006,7 +3007,7 @@
         <v>25020690,1974,80</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A171" s="1">
         <v>25020690</v>
       </c>
@@ -3021,7 +3022,7 @@
         <v>25020690,1975,80</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A172" s="1">
         <v>25020690</v>
       </c>
@@ -3036,7 +3037,7 @@
         <v>25020690,1976,92</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A173" s="1">
         <v>25020690</v>
       </c>
@@ -3051,7 +3052,7 @@
         <v>25020690,1977,57</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A174" s="1">
         <v>25020690</v>
       </c>
@@ -3066,7 +3067,7 @@
         <v>25020690,1978,55</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A175" s="1">
         <v>25020690</v>
       </c>
@@ -3081,7 +3082,7 @@
         <v>25020690,1979,66</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A176" s="1">
         <v>25020690</v>
       </c>
@@ -3096,7 +3097,7 @@
         <v>25020690,1980,135</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A177" s="1">
         <v>25020690</v>
       </c>
@@ -3111,7 +3112,7 @@
         <v>25020690,1981,117</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A178" s="1">
         <v>25020690</v>
       </c>
@@ -3126,7 +3127,7 @@
         <v>25020690,1982,72</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A179" s="1">
         <v>25020690</v>
       </c>
@@ -3141,7 +3142,7 @@
         <v>25020690,1983,96</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A180" s="1">
         <v>25020690</v>
       </c>
@@ -3156,7 +3157,7 @@
         <v>25020690,1984,116</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A181" s="1">
         <v>25020690</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>25020690,1985,70</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A182" s="1">
         <v>25020690</v>
       </c>
@@ -3186,7 +3187,7 @@
         <v>25020690,1986,53</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A183" s="1">
         <v>25020690</v>
       </c>
@@ -3201,7 +3202,7 @@
         <v>25020690,1987,15</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A184" s="1">
         <v>25020690</v>
       </c>
@@ -3216,7 +3217,7 @@
         <v>25020690,1988,125</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A185" s="1">
         <v>25020690</v>
       </c>
@@ -3231,7 +3232,7 @@
         <v>25020690,1989,145</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A186" s="1">
         <v>25020690</v>
       </c>
@@ -3246,7 +3247,7 @@
         <v>25020690,1990,80</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A187" s="1">
         <v>25020690</v>
       </c>
@@ -3261,7 +3262,7 @@
         <v>25020690,1991,80</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A188" s="1">
         <v>25020690</v>
       </c>
@@ -3276,7 +3277,7 @@
         <v>25020690,1992,90</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A189" s="1">
         <v>25020690</v>
       </c>
@@ -3291,7 +3292,7 @@
         <v>25020690,1993,125</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A190" s="1">
         <v>25020690</v>
       </c>
@@ -3306,7 +3307,7 @@
         <v>25020690,1994,80</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A191" s="1">
         <v>25020690</v>
       </c>
@@ -3321,7 +3322,7 @@
         <v>25020690,1995,90</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A192" s="1">
         <v>25020690</v>
       </c>
@@ -3336,7 +3337,7 @@
         <v>25020690,1996,90</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A193" s="1">
         <v>25020690</v>
       </c>
@@ -3351,7 +3352,7 @@
         <v>25020690,1997,80</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A194" s="1">
         <v>25020690</v>
       </c>
@@ -3366,7 +3367,7 @@
         <v>25020690,1998,60</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A195" s="1">
         <v>25020690</v>
       </c>
@@ -3381,7 +3382,7 @@
         <v>25020690,1999,95</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A196" s="1">
         <v>25020690</v>
       </c>
@@ -3396,7 +3397,7 @@
         <v>25020690,2000,90</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A197" s="1">
         <v>25020690</v>
       </c>
@@ -3411,7 +3412,7 @@
         <v>25020690,2001,98</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A198" s="1">
         <v>25020690</v>
       </c>
@@ -3426,7 +3427,7 @@
         <v>25020690,2002,135</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A199" s="1">
         <v>25020690</v>
       </c>
@@ -3441,7 +3442,7 @@
         <v>25020690,2003,90</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A200" s="1">
         <v>25020690</v>
       </c>
@@ -3456,7 +3457,7 @@
         <v>25020690,2004,98</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A201" s="1">
         <v>25020690</v>
       </c>
@@ -3471,7 +3472,7 @@
         <v>25020690,2005,133</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A202" s="1">
         <v>25020690</v>
       </c>
@@ -3486,7 +3487,7 @@
         <v>25020690,2006,90</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A203" s="1">
         <v>25020690</v>
       </c>
@@ -3501,7 +3502,7 @@
         <v>25020690,2007,99</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A204" s="1">
         <v>25020690</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>25020690,2008,100</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A205" s="1">
         <v>25020690</v>
       </c>
@@ -3531,7 +3532,7 @@
         <v>25020690,2009,90</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A206" s="1">
         <v>28020080</v>
       </c>
@@ -3546,7 +3547,7 @@
         <v>28020080,1959,65</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A207" s="1">
         <v>28020080</v>
       </c>
@@ -3561,7 +3562,7 @@
         <v>28020080,1960,53</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A208" s="1">
         <v>28020080</v>
       </c>
@@ -3573,7 +3574,7 @@
         <v>28020080,1961,</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A209" s="1">
         <v>28020080</v>
       </c>
@@ -3588,7 +3589,7 @@
         <v>28020080,1962,114</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A210" s="1">
         <v>28020080</v>
       </c>
@@ -3603,7 +3604,7 @@
         <v>28020080,1963,79</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A211" s="1">
         <v>28020080</v>
       </c>
@@ -3618,7 +3619,7 @@
         <v>28020080,1964,72</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A212" s="1">
         <v>28020080</v>
       </c>
@@ -3633,7 +3634,7 @@
         <v>28020080,1965,11</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A213" s="1">
         <v>28020080</v>
       </c>
@@ -3645,7 +3646,7 @@
         <v>28020080,1966,</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A214" s="1">
         <v>28020080</v>
       </c>
@@ -3657,7 +3658,7 @@
         <v>28020080,1967,</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A215" s="1">
         <v>28020080</v>
       </c>
@@ -3672,7 +3673,7 @@
         <v>28020080,1968,72</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A216" s="1">
         <v>28020080</v>
       </c>
@@ -3687,7 +3688,7 @@
         <v>28020080,1969,99</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A217" s="1">
         <v>28020080</v>
       </c>
@@ -3702,7 +3703,7 @@
         <v>28020080,1970,100</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A218" s="1">
         <v>28020080</v>
       </c>
@@ -3717,7 +3718,7 @@
         <v>28020080,1971,80</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A219" s="1">
         <v>28020080</v>
       </c>
@@ -3732,7 +3733,7 @@
         <v>28020080,1972,100</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A220" s="1">
         <v>28020080</v>
       </c>
@@ -3747,7 +3748,7 @@
         <v>28020080,1973,96</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A221" s="1">
         <v>28020080</v>
       </c>
@@ -3762,7 +3763,7 @@
         <v>28020080,1974,55</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A222" s="1">
         <v>28020080</v>
       </c>
@@ -3777,7 +3778,7 @@
         <v>28020080,1975,130</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A223" s="1">
         <v>28020080</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>28020080,1976,82</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A224" s="1">
         <v>28020080</v>
       </c>
@@ -3804,7 +3805,7 @@
         <v>28020080,1977,</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A225" s="1">
         <v>28020080</v>
       </c>
@@ -3816,7 +3817,7 @@
         <v>28020080,1978,</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A226" s="1">
         <v>28020080</v>
       </c>
@@ -3831,7 +3832,7 @@
         <v>28020080,1979,66</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A227" s="1">
         <v>28020080</v>
       </c>
@@ -3846,7 +3847,7 @@
         <v>28020080,1980,90</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A228" s="1">
         <v>28020080</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>28020080,1981,90</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A229" s="1">
         <v>28020080</v>
       </c>
@@ -3876,7 +3877,7 @@
         <v>28020080,1982,60</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A230" s="1">
         <v>28020080</v>
       </c>
@@ -3891,7 +3892,7 @@
         <v>28020080,1983,106</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A231" s="1">
         <v>28020080</v>
       </c>
@@ -3906,7 +3907,7 @@
         <v>28020080,1984,230.2</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A232" s="1">
         <v>28020080</v>
       </c>
@@ -3921,7 +3922,7 @@
         <v>28020080,1985,162</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A233" s="1">
         <v>28020080</v>
       </c>
@@ -3936,7 +3937,7 @@
         <v>28020080,1986,80</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A234" s="1">
         <v>28020080</v>
       </c>
@@ -3948,7 +3949,7 @@
         <v>28020080,1987,</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A235" s="1">
         <v>28020080</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v>28020080,1988,75</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A236" s="1">
         <v>28020080</v>
       </c>
@@ -3978,7 +3979,7 @@
         <v>28020080,1989,70</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A237" s="1">
         <v>28020080</v>
       </c>
@@ -3993,7 +3994,7 @@
         <v>28020080,1990,70</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A238" s="1">
         <v>28020080</v>
       </c>
@@ -4008,7 +4009,7 @@
         <v>28020080,1991,70</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A239" s="1">
         <v>28020080</v>
       </c>
@@ -4023,7 +4024,7 @@
         <v>28020080,1992,77</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A240" s="1">
         <v>28020080</v>
       </c>
@@ -4038,7 +4039,7 @@
         <v>28020080,1993,112</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A241" s="1">
         <v>28020080</v>
       </c>
@@ -4053,7 +4054,7 @@
         <v>28020080,1994,80</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A242" s="1">
         <v>28020080</v>
       </c>
@@ -4068,7 +4069,7 @@
         <v>28020080,1995,115</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A243" s="1">
         <v>28020080</v>
       </c>
@@ -4083,7 +4084,7 @@
         <v>28020080,1996,123</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A244" s="1">
         <v>28020080</v>
       </c>
@@ -4098,7 +4099,7 @@
         <v>28020080,1997,65</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A245" s="1">
         <v>28020080</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>28020080,1998,140</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A246" s="1">
         <v>28020080</v>
       </c>
@@ -4128,7 +4129,7 @@
         <v>28020080,1999,90</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A247" s="1">
         <v>28020080</v>
       </c>
@@ -4143,7 +4144,7 @@
         <v>28020080,2000,120</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A248" s="1">
         <v>28020080</v>
       </c>
@@ -4158,7 +4159,7 @@
         <v>28020080,2001,110</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A249" s="1">
         <v>28020080</v>
       </c>
@@ -4173,7 +4174,7 @@
         <v>28020080,2002,94</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A250" s="1">
         <v>28020080</v>
       </c>
@@ -4188,7 +4189,7 @@
         <v>28020080,2003,53</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A251" s="1">
         <v>28020080</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>28020080,2004,89</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A252" s="1">
         <v>28020080</v>
       </c>
@@ -4218,7 +4219,7 @@
         <v>28020080,2005,151</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A253" s="1">
         <v>28020080</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>28020080,2006,97</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A254" s="1">
         <v>28020080</v>
       </c>
@@ -4248,7 +4249,7 @@
         <v>28020080,2007,100</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A255" s="1">
         <v>28020080</v>
       </c>
@@ -4263,7 +4264,7 @@
         <v>28020080,2008,220</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A256" s="1">
         <v>28020080</v>
       </c>
@@ -4278,7 +4279,7 @@
         <v>28020080,2009,68</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A257" s="1">
         <v>28020230</v>
       </c>
@@ -4290,7 +4291,7 @@
         <v>28020230,1959,</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A258" s="1">
         <v>28020230</v>
       </c>
@@ -4302,7 +4303,7 @@
         <v>28020230,1960,</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="259" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A259" s="1">
         <v>28020230</v>
       </c>
@@ -4314,7 +4315,7 @@
         <v>28020230,1961,</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="260" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A260" s="1">
         <v>28020230</v>
       </c>
@@ -4326,7 +4327,7 @@
         <v>28020230,1962,</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="261" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A261" s="1">
         <v>28020230</v>
       </c>
@@ -4338,7 +4339,7 @@
         <v>28020230,1963,</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="262" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A262" s="1">
         <v>28020230</v>
       </c>
@@ -4350,7 +4351,7 @@
         <v>28020230,1964,</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="263" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A263" s="1">
         <v>28020230</v>
       </c>
@@ -4362,7 +4363,7 @@
         <v>28020230,1965,</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="264" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A264" s="1">
         <v>28020230</v>
       </c>
@@ -4374,7 +4375,7 @@
         <v>28020230,1966,</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="265" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A265" s="1">
         <v>28020230</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>28020230,1967,</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="266" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A266" s="1">
         <v>28020230</v>
       </c>
@@ -4398,7 +4399,7 @@
         <v>28020230,1968,</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="267" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A267" s="1">
         <v>28020230</v>
       </c>
@@ -4413,7 +4414,7 @@
         <v>28020230,1969,90</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="268" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A268" s="1">
         <v>28020230</v>
       </c>
@@ -4428,7 +4429,7 @@
         <v>28020230,1970,86</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="269" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A269" s="1">
         <v>28020230</v>
       </c>
@@ -4443,7 +4444,7 @@
         <v>28020230,1971,114</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="270" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A270" s="1">
         <v>28020230</v>
       </c>
@@ -4458,7 +4459,7 @@
         <v>28020230,1972,53</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="271" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A271" s="1">
         <v>28020230</v>
       </c>
@@ -4473,7 +4474,7 @@
         <v>28020230,1973,130</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="272" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A272" s="1">
         <v>28020230</v>
       </c>
@@ -4488,7 +4489,7 @@
         <v>28020230,1974,109</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="273" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A273" s="1">
         <v>28020230</v>
       </c>
@@ -4503,7 +4504,7 @@
         <v>28020230,1975,115</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="274" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A274" s="1">
         <v>28020230</v>
       </c>
@@ -4518,7 +4519,7 @@
         <v>28020230,1976,100</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="275" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A275" s="1">
         <v>28020230</v>
       </c>
@@ -4533,7 +4534,7 @@
         <v>28020230,1977,90</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="276" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A276" s="1">
         <v>28020230</v>
       </c>
@@ -4548,7 +4549,7 @@
         <v>28020230,1978,100</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="277" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A277" s="1">
         <v>28020230</v>
       </c>
@@ -4563,7 +4564,7 @@
         <v>28020230,1979,93</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="278" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A278" s="1">
         <v>28020230</v>
       </c>
@@ -4578,7 +4579,7 @@
         <v>28020230,1980,127</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="279" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A279" s="1">
         <v>28020230</v>
       </c>
@@ -4593,7 +4594,7 @@
         <v>28020230,1981,137</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="280" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A280" s="1">
         <v>28020230</v>
       </c>
@@ -4608,7 +4609,7 @@
         <v>28020230,1982,110</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="281" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A281" s="1">
         <v>28020230</v>
       </c>
@@ -4623,7 +4624,7 @@
         <v>28020230,1983,114.7</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="282" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A282" s="1">
         <v>28020230</v>
       </c>
@@ -4638,7 +4639,7 @@
         <v>28020230,1984,80.2</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="283" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A283" s="1">
         <v>28020230</v>
       </c>
@@ -4653,7 +4654,7 @@
         <v>28020230,1985,127</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="284" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A284" s="1">
         <v>28020230</v>
       </c>
@@ -4668,7 +4669,7 @@
         <v>28020230,1986,135.6</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="285" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A285" s="1">
         <v>28020230</v>
       </c>
@@ -4683,7 +4684,7 @@
         <v>28020230,1987,141.7</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="286" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A286" s="1">
         <v>28020230</v>
       </c>
@@ -4698,7 +4699,7 @@
         <v>28020230,1988,86.5</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="287" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A287" s="1">
         <v>28020230</v>
       </c>
@@ -4713,7 +4714,7 @@
         <v>28020230,1989,67</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="288" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A288" s="1">
         <v>28020230</v>
       </c>
@@ -4728,7 +4729,7 @@
         <v>28020230,1990,34.3</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="289" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A289" s="1">
         <v>28020230</v>
       </c>
@@ -4743,7 +4744,7 @@
         <v>28020230,1991,94</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="290" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A290" s="1">
         <v>28020230</v>
       </c>
@@ -4758,7 +4759,7 @@
         <v>28020230,1992,91</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="291" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A291" s="1">
         <v>28020230</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>28020230,1993,90</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="292" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A292" s="1">
         <v>28020230</v>
       </c>
@@ -4788,7 +4789,7 @@
         <v>28020230,1994,90</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="293" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A293" s="1">
         <v>28020230</v>
       </c>
@@ -4803,7 +4804,7 @@
         <v>28020230,1995,200</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="294" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A294" s="1">
         <v>28020230</v>
       </c>
@@ -4818,7 +4819,7 @@
         <v>28020230,1996,89</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="295" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A295" s="1">
         <v>28020230</v>
       </c>
@@ -4833,7 +4834,7 @@
         <v>28020230,1997,75</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="296" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A296" s="1">
         <v>28020230</v>
       </c>
@@ -4848,7 +4849,7 @@
         <v>28020230,1998,90</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="297" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A297" s="1">
         <v>28020230</v>
       </c>
@@ -4863,7 +4864,7 @@
         <v>28020230,1999,137</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="298" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A298" s="1">
         <v>28020230</v>
       </c>
@@ -4878,7 +4879,7 @@
         <v>28020230,2000,125</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="299" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A299" s="1">
         <v>28020230</v>
       </c>
@@ -4893,7 +4894,7 @@
         <v>28020230,2001,78</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="300" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A300" s="1">
         <v>28020230</v>
       </c>
@@ -4905,7 +4906,7 @@
         <v>28020230,2002,</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="301" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A301" s="1">
         <v>28020230</v>
       </c>
@@ -4917,7 +4918,7 @@
         <v>28020230,2003,</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="302" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A302" s="1">
         <v>28020230</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>28020230,2004,</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A303" s="1">
         <v>28020230</v>
       </c>
@@ -4941,7 +4942,7 @@
         <v>28020230,2005,</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A304" s="1">
         <v>28020230</v>
       </c>
@@ -4953,7 +4954,7 @@
         <v>28020230,2006,</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A305" s="1">
         <v>28020230</v>
       </c>
@@ -4965,7 +4966,7 @@
         <v>28020230,2007,</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A306" s="1">
         <v>28020230</v>
       </c>
@@ -4977,7 +4978,7 @@
         <v>28020230,2008,</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A307" s="1">
         <v>28020230</v>
       </c>
@@ -4989,7 +4990,7 @@
         <v>28020230,2009,</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A308" s="1">
         <v>28020260</v>
       </c>
@@ -5001,7 +5002,7 @@
         <v>28020260,1959,</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A309" s="1">
         <v>28020260</v>
       </c>
@@ -5013,7 +5014,7 @@
         <v>28020260,1960,</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A310" s="1">
         <v>28020260</v>
       </c>
@@ -5025,7 +5026,7 @@
         <v>28020260,1961,</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A311" s="1">
         <v>28020260</v>
       </c>
@@ -5037,7 +5038,7 @@
         <v>28020260,1962,</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A312" s="1">
         <v>28020260</v>
       </c>
@@ -5049,7 +5050,7 @@
         <v>28020260,1963,</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A313" s="1">
         <v>28020260</v>
       </c>
@@ -5061,7 +5062,7 @@
         <v>28020260,1964,</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="314" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A314" s="1">
         <v>28020260</v>
       </c>
@@ -5073,7 +5074,7 @@
         <v>28020260,1965,</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A315" s="1">
         <v>28020260</v>
       </c>
@@ -5085,7 +5086,7 @@
         <v>28020260,1966,</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A316" s="1">
         <v>28020260</v>
       </c>
@@ -5097,7 +5098,7 @@
         <v>28020260,1967,</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A317" s="1">
         <v>28020260</v>
       </c>
@@ -5109,7 +5110,7 @@
         <v>28020260,1968,</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A318" s="1">
         <v>28020260</v>
       </c>
@@ -5124,7 +5125,7 @@
         <v>28020260,1969,92</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A319" s="1">
         <v>28020260</v>
       </c>
@@ -5139,7 +5140,7 @@
         <v>28020260,1970,160</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A320" s="1">
         <v>28020260</v>
       </c>
@@ -5154,7 +5155,7 @@
         <v>28020260,1971,96</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A321" s="1">
         <v>28020260</v>
       </c>
@@ -5166,7 +5167,7 @@
         <v>28020260,1972,</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A322" s="1">
         <v>28020260</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>28020260,1973,</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A323" s="1">
         <v>28020260</v>
       </c>
@@ -5190,7 +5191,7 @@
         <v>28020260,1974,</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A324" s="1">
         <v>28020260</v>
       </c>
@@ -5202,7 +5203,7 @@
         <v>28020260,1975,</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A325" s="1">
         <v>28020260</v>
       </c>
@@ -5214,7 +5215,7 @@
         <v>28020260,1976,</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A326" s="1">
         <v>28020260</v>
       </c>
@@ -5226,7 +5227,7 @@
         <v>28020260,1977,</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A327" s="1">
         <v>28020260</v>
       </c>
@@ -5238,7 +5239,7 @@
         <v>28020260,1978,</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A328" s="1">
         <v>28020260</v>
       </c>
@@ -5250,7 +5251,7 @@
         <v>28020260,1979,</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A329" s="1">
         <v>28020260</v>
       </c>
@@ -5262,7 +5263,7 @@
         <v>28020260,1980,</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A330" s="1">
         <v>28020260</v>
       </c>
@@ -5274,7 +5275,7 @@
         <v>28020260,1981,</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A331" s="1">
         <v>28020260</v>
       </c>
@@ -5286,7 +5287,7 @@
         <v>28020260,1982,</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A332" s="1">
         <v>28020260</v>
       </c>
@@ -5298,7 +5299,7 @@
         <v>28020260,1983,</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A333" s="1">
         <v>28020260</v>
       </c>
@@ -5310,7 +5311,7 @@
         <v>28020260,1984,</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A334" s="1">
         <v>28020260</v>
       </c>
@@ -5322,7 +5323,7 @@
         <v>28020260,1985,</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A335" s="1">
         <v>28020260</v>
       </c>
@@ -5334,7 +5335,7 @@
         <v>28020260,1986,</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A336" s="1">
         <v>28020260</v>
       </c>
@@ -5346,7 +5347,7 @@
         <v>28020260,1987,</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A337" s="1">
         <v>28020260</v>
       </c>
@@ -5358,7 +5359,7 @@
         <v>28020260,1988,</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A338" s="1">
         <v>28020260</v>
       </c>
@@ -5370,7 +5371,7 @@
         <v>28020260,1989,</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A339" s="1">
         <v>28020260</v>
       </c>
@@ -5382,7 +5383,7 @@
         <v>28020260,1990,</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A340" s="1">
         <v>28020260</v>
       </c>
@@ -5394,7 +5395,7 @@
         <v>28020260,1991,</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A341" s="1">
         <v>28020260</v>
       </c>
@@ -5406,7 +5407,7 @@
         <v>28020260,1992,</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A342" s="1">
         <v>28020260</v>
       </c>
@@ -5418,7 +5419,7 @@
         <v>28020260,1993,</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A343" s="1">
         <v>28020260</v>
       </c>
@@ -5430,7 +5431,7 @@
         <v>28020260,1994,</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A344" s="1">
         <v>28020260</v>
       </c>
@@ -5442,7 +5443,7 @@
         <v>28020260,1995,</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A345" s="1">
         <v>28020260</v>
       </c>
@@ -5454,7 +5455,7 @@
         <v>28020260,1996,</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A346" s="1">
         <v>28020260</v>
       </c>
@@ -5466,7 +5467,7 @@
         <v>28020260,1997,</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A347" s="1">
         <v>28020260</v>
       </c>
@@ -5478,7 +5479,7 @@
         <v>28020260,1998,</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A348" s="1">
         <v>28020260</v>
       </c>
@@ -5490,7 +5491,7 @@
         <v>28020260,1999,</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A349" s="1">
         <v>28020260</v>
       </c>
@@ -5502,7 +5503,7 @@
         <v>28020260,2000,</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A350" s="1">
         <v>28020260</v>
       </c>
@@ -5514,7 +5515,7 @@
         <v>28020260,2001,</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A351" s="1">
         <v>28020260</v>
       </c>
@@ -5526,7 +5527,7 @@
         <v>28020260,2002,</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A352" s="1">
         <v>28020260</v>
       </c>
@@ -5538,7 +5539,7 @@
         <v>28020260,2003,</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A353" s="1">
         <v>28020260</v>
       </c>
@@ -5550,7 +5551,7 @@
         <v>28020260,2004,</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A354" s="1">
         <v>28020260</v>
       </c>
@@ -5562,7 +5563,7 @@
         <v>28020260,2005,</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A355" s="1">
         <v>28020260</v>
       </c>
@@ -5574,7 +5575,7 @@
         <v>28020260,2006,</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A356" s="1">
         <v>28020260</v>
       </c>
@@ -5586,7 +5587,7 @@
         <v>28020260,2007,</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A357" s="1">
         <v>28020260</v>
       </c>
@@ -5598,7 +5599,7 @@
         <v>28020260,2008,</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A358" s="1">
         <v>28020260</v>
       </c>
@@ -5610,7 +5611,7 @@
         <v>28020260,2009,</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A359" s="1">
         <v>28020440</v>
       </c>
@@ -5625,7 +5626,7 @@
         <v>28020440,1959,135</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A360" s="1">
         <v>28020440</v>
       </c>
@@ -5640,7 +5641,7 @@
         <v>28020440,1960,100</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A361" s="1">
         <v>28020440</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>28020440,1961,52</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A362" s="1">
         <v>28020440</v>
       </c>
@@ -5667,7 +5668,7 @@
         <v>28020440,1962,</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A363" s="1">
         <v>28020440</v>
       </c>
@@ -5682,7 +5683,7 @@
         <v>28020440,1963,85</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A364" s="1">
         <v>28020440</v>
       </c>
@@ -5697,7 +5698,7 @@
         <v>28020440,1964,73</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A365" s="1">
         <v>28020440</v>
       </c>
@@ -5712,7 +5713,7 @@
         <v>28020440,1965,117</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A366" s="1">
         <v>28020440</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>28020440,1966,</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A367" s="1">
         <v>28020440</v>
       </c>
@@ -5739,7 +5740,7 @@
         <v>28020440,1967,79</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A368" s="1">
         <v>28020440</v>
       </c>
@@ -5754,7 +5755,7 @@
         <v>28020440,1968,95</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A369" s="1">
         <v>28020440</v>
       </c>
@@ -5769,7 +5770,7 @@
         <v>28020440,1969,97</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A370" s="1">
         <v>28020440</v>
       </c>
@@ -5784,7 +5785,7 @@
         <v>28020440,1970,133</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A371" s="1">
         <v>28020440</v>
       </c>
@@ -5799,7 +5800,7 @@
         <v>28020440,1971,103</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A372" s="1">
         <v>28020440</v>
       </c>
@@ -5814,7 +5815,7 @@
         <v>28020440,1972,136</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A373" s="1">
         <v>28020440</v>
       </c>
@@ -5829,7 +5830,7 @@
         <v>28020440,1973,134</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A374" s="1">
         <v>28020440</v>
       </c>
@@ -5844,7 +5845,7 @@
         <v>28020440,1974,76</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A375" s="1">
         <v>28020440</v>
       </c>
@@ -5859,7 +5860,7 @@
         <v>28020440,1975,100</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A376" s="1">
         <v>28020440</v>
       </c>
@@ -5874,7 +5875,7 @@
         <v>28020440,1976,84</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A377" s="1">
         <v>28020440</v>
       </c>
@@ -5889,7 +5890,7 @@
         <v>28020440,1977,86</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A378" s="1">
         <v>28020440</v>
       </c>
@@ -5904,7 +5905,7 @@
         <v>28020440,1978,93</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A379" s="1">
         <v>28020440</v>
       </c>
@@ -5919,7 +5920,7 @@
         <v>28020440,1979,105</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A380" s="1">
         <v>28020440</v>
       </c>
@@ -5934,7 +5935,7 @@
         <v>28020440,1980,126</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A381" s="1">
         <v>28020440</v>
       </c>
@@ -5949,7 +5950,7 @@
         <v>28020440,1981,106</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A382" s="1">
         <v>28020440</v>
       </c>
@@ -5964,7 +5965,7 @@
         <v>28020440,1982,84</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A383" s="1">
         <v>28020440</v>
       </c>
@@ -5979,7 +5980,7 @@
         <v>28020440,1983,100.5</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A384" s="1">
         <v>28020440</v>
       </c>
@@ -5994,7 +5995,7 @@
         <v>28020440,1984,97.6</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A385" s="1">
         <v>28020440</v>
       </c>
@@ -6009,7 +6010,7 @@
         <v>28020440,1985,118.6</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A386" s="1">
         <v>28020440</v>
       </c>
@@ -6024,7 +6025,7 @@
         <v>28020440,1986,114</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A387" s="1">
         <v>28020440</v>
       </c>
@@ -6039,7 +6040,7 @@
         <v>28020440,1987,123.2</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A388" s="1">
         <v>28020440</v>
       </c>
@@ -6054,7 +6055,7 @@
         <v>28020440,1988,134</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A389" s="1">
         <v>28020440</v>
       </c>
@@ -6069,7 +6070,7 @@
         <v>28020440,1989,83.7</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A390" s="1">
         <v>28020440</v>
       </c>
@@ -6084,7 +6085,7 @@
         <v>28020440,1990,86.4</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A391" s="1">
         <v>28020440</v>
       </c>
@@ -6099,7 +6100,7 @@
         <v>28020440,1991,74.5</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A392" s="1">
         <v>28020440</v>
       </c>
@@ -6114,7 +6115,7 @@
         <v>28020440,1992,80.5</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A393" s="1">
         <v>28020440</v>
       </c>
@@ -6129,7 +6130,7 @@
         <v>28020440,1993,86.5</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A394" s="1">
         <v>28020440</v>
       </c>
@@ -6144,7 +6145,7 @@
         <v>28020440,1994,65</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A395" s="1">
         <v>28020440</v>
       </c>
@@ -6159,7 +6160,7 @@
         <v>28020440,1995,98</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A396" s="1">
         <v>28020440</v>
       </c>
@@ -6174,7 +6175,7 @@
         <v>28020440,1996,118</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A397" s="1">
         <v>28020440</v>
       </c>
@@ -6189,7 +6190,7 @@
         <v>28020440,1997,25</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A398" s="1">
         <v>28020440</v>
       </c>
@@ -6204,7 +6205,7 @@
         <v>28020440,1998,94</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A399" s="1">
         <v>28020440</v>
       </c>
@@ -6219,7 +6220,7 @@
         <v>28020440,1999,102</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A400" s="1">
         <v>28020440</v>
       </c>
@@ -6234,7 +6235,7 @@
         <v>28020440,2000,94</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A401" s="1">
         <v>28020440</v>
       </c>
@@ -6249,7 +6250,7 @@
         <v>28020440,2001,82</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A402" s="1">
         <v>28020440</v>
       </c>
@@ -6264,7 +6265,7 @@
         <v>28020440,2002,87</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A403" s="1">
         <v>28020440</v>
       </c>
@@ -6279,7 +6280,7 @@
         <v>28020440,2003,29</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A404" s="1">
         <v>28020440</v>
       </c>
@@ -6294,7 +6295,7 @@
         <v>28020440,2004,81</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A405" s="1">
         <v>28020440</v>
       </c>
@@ -6309,7 +6310,7 @@
         <v>28020440,2005,62</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A406" s="1">
         <v>28020440</v>
       </c>
@@ -6324,7 +6325,7 @@
         <v>28020440,2006,92</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A407" s="1">
         <v>28020440</v>
       </c>
@@ -6339,7 +6340,7 @@
         <v>28020440,2007,143</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A408" s="1">
         <v>28020440</v>
       </c>
@@ -6354,7 +6355,7 @@
         <v>28020440,2008,87</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A409" s="1">
         <v>28020440</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>28020440,2009,82</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A410" s="1">
         <v>28020600</v>
       </c>
@@ -6381,7 +6382,7 @@
         <v>28020600,1959,</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A411" s="1">
         <v>28020600</v>
       </c>
@@ -6393,7 +6394,7 @@
         <v>28020600,1960,</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A412" s="1">
         <v>28020600</v>
       </c>
@@ -6405,7 +6406,7 @@
         <v>28020600,1961,</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A413" s="1">
         <v>28020600</v>
       </c>
@@ -6417,7 +6418,7 @@
         <v>28020600,1962,</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A414" s="1">
         <v>28020600</v>
       </c>
@@ -6429,7 +6430,7 @@
         <v>28020600,1963,</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A415" s="1">
         <v>28020600</v>
       </c>
@@ -6441,7 +6442,7 @@
         <v>28020600,1964,</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A416" s="1">
         <v>28020600</v>
       </c>
@@ -6453,7 +6454,7 @@
         <v>28020600,1965,</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A417" s="1">
         <v>28020600</v>
       </c>
@@ -6465,7 +6466,7 @@
         <v>28020600,1966,</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A418" s="1">
         <v>28020600</v>
       </c>
@@ -6477,7 +6478,7 @@
         <v>28020600,1967,</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A419" s="1">
         <v>28020600</v>
       </c>
@@ -6489,7 +6490,7 @@
         <v>28020600,1968,</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A420" s="1">
         <v>28020600</v>
       </c>
@@ -6501,7 +6502,7 @@
         <v>28020600,1969,</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A421" s="1">
         <v>28020600</v>
       </c>
@@ -6513,7 +6514,7 @@
         <v>28020600,1970,</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A422" s="1">
         <v>28020600</v>
       </c>
@@ -6525,7 +6526,7 @@
         <v>28020600,1971,</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A423" s="1">
         <v>28020600</v>
       </c>
@@ -6537,7 +6538,7 @@
         <v>28020600,1972,</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A424" s="1">
         <v>28020600</v>
       </c>
@@ -6549,7 +6550,7 @@
         <v>28020600,1973,</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A425" s="1">
         <v>28020600</v>
       </c>
@@ -6561,7 +6562,7 @@
         <v>28020600,1974,</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A426" s="1">
         <v>28020600</v>
       </c>
@@ -6573,7 +6574,7 @@
         <v>28020600,1975,</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A427" s="1">
         <v>28020600</v>
       </c>
@@ -6585,7 +6586,7 @@
         <v>28020600,1976,</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A428" s="1">
         <v>28020600</v>
       </c>
@@ -6597,7 +6598,7 @@
         <v>28020600,1977,</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A429" s="1">
         <v>28020600</v>
       </c>
@@ -6609,7 +6610,7 @@
         <v>28020600,1978,</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A430" s="1">
         <v>28020600</v>
       </c>
@@ -6621,7 +6622,7 @@
         <v>28020600,1979,</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A431" s="1">
         <v>28020600</v>
       </c>
@@ -6633,7 +6634,7 @@
         <v>28020600,1980,</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A432" s="1">
         <v>28020600</v>
       </c>
@@ -6648,7 +6649,7 @@
         <v>28020600,1981,28</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A433" s="1">
         <v>28020600</v>
       </c>
@@ -6663,7 +6664,7 @@
         <v>28020600,1982,118</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A434" s="1">
         <v>28020600</v>
       </c>
@@ -6678,7 +6679,7 @@
         <v>28020600,1983,80</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A435" s="1">
         <v>28020600</v>
       </c>
@@ -6693,7 +6694,7 @@
         <v>28020600,1984,67</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A436" s="1">
         <v>28020600</v>
       </c>
@@ -6708,7 +6709,7 @@
         <v>28020600,1985,97</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A437" s="1">
         <v>28020600</v>
       </c>
@@ -6723,7 +6724,7 @@
         <v>28020600,1986,98</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A438" s="1">
         <v>28020600</v>
       </c>
@@ -6738,7 +6739,7 @@
         <v>28020600,1987,93</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A439" s="1">
         <v>28020600</v>
       </c>
@@ -6753,7 +6754,7 @@
         <v>28020600,1988,82</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A440" s="1">
         <v>28020600</v>
       </c>
@@ -6768,7 +6769,7 @@
         <v>28020600,1989,93</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A441" s="1">
         <v>28020600</v>
       </c>
@@ -6783,7 +6784,7 @@
         <v>28020600,1990,113</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A442" s="1">
         <v>28020600</v>
       </c>
@@ -6798,7 +6799,7 @@
         <v>28020600,1991,112.1</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A443" s="1">
         <v>28020600</v>
       </c>
@@ -6813,7 +6814,7 @@
         <v>28020600,1992,75</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A444" s="1">
         <v>28020600</v>
       </c>
@@ -6828,7 +6829,7 @@
         <v>28020600,1993,95</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A445" s="1">
         <v>28020600</v>
       </c>
@@ -6843,7 +6844,7 @@
         <v>28020600,1994,100.3</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A446" s="1">
         <v>28020600</v>
       </c>
@@ -6858,7 +6859,7 @@
         <v>28020600,1995,135.1</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A447" s="1">
         <v>28020600</v>
       </c>
@@ -6873,7 +6874,7 @@
         <v>28020600,1996,85.4</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A448" s="1">
         <v>28020600</v>
       </c>
@@ -6888,7 +6889,7 @@
         <v>28020600,1997,73</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A449" s="1">
         <v>28020600</v>
       </c>
@@ -6903,7 +6904,7 @@
         <v>28020600,1998,110</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A450" s="1">
         <v>28020600</v>
       </c>
@@ -6918,7 +6919,7 @@
         <v>28020600,1999,99</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A451" s="1">
         <v>28020600</v>
       </c>
@@ -6933,7 +6934,7 @@
         <v>28020600,2000,94.7</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A452" s="1">
         <v>28020600</v>
       </c>
@@ -6948,7 +6949,7 @@
         <v>28020600,2001,43.4</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A453" s="1">
         <v>28020600</v>
       </c>
@@ -6963,7 +6964,7 @@
         <v>28020600,2002,98</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A454" s="1">
         <v>28020600</v>
       </c>
@@ -6978,7 +6979,7 @@
         <v>28020600,2003,79.2</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A455" s="1">
         <v>28020600</v>
       </c>
@@ -6993,7 +6994,7 @@
         <v>28020600,2004,97</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A456" s="1">
         <v>28020600</v>
       </c>
@@ -7005,7 +7006,7 @@
         <v>28020600,2005,</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A457" s="1">
         <v>28020600</v>
       </c>
@@ -7017,7 +7018,7 @@
         <v>28020600,2006,</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A458" s="1">
         <v>28020600</v>
       </c>
@@ -7029,7 +7030,7 @@
         <v>28020600,2007,</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A459" s="1">
         <v>28020600</v>
       </c>
@@ -7041,7 +7042,7 @@
         <v>28020600,2008,</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A460" s="1">
         <v>28020600</v>
       </c>
@@ -7056,7 +7057,7 @@
         <v>28020600,2009,81</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A461" s="1">
         <v>28025080</v>
       </c>
@@ -7068,7 +7069,7 @@
         <v>28025080,1959,</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A462" s="1">
         <v>28025080</v>
       </c>
@@ -7080,7 +7081,7 @@
         <v>28025080,1960,</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A463" s="1">
         <v>28025080</v>
       </c>
@@ -7092,7 +7093,7 @@
         <v>28025080,1961,</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A464" s="1">
         <v>28025080</v>
       </c>
@@ -7104,7 +7105,7 @@
         <v>28025080,1962,</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A465" s="1">
         <v>28025080</v>
       </c>
@@ -7116,7 +7117,7 @@
         <v>28025080,1963,</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A466" s="1">
         <v>28025080</v>
       </c>
@@ -7128,7 +7129,7 @@
         <v>28025080,1964,</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A467" s="1">
         <v>28025080</v>
       </c>
@@ -7140,7 +7141,7 @@
         <v>28025080,1965,</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A468" s="1">
         <v>28025080</v>
       </c>
@@ -7152,7 +7153,7 @@
         <v>28025080,1966,</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A469" s="1">
         <v>28025080</v>
       </c>
@@ -7164,7 +7165,7 @@
         <v>28025080,1967,</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A470" s="1">
         <v>28025080</v>
       </c>
@@ -7176,7 +7177,7 @@
         <v>28025080,1968,</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A471" s="1">
         <v>28025080</v>
       </c>
@@ -7188,7 +7189,7 @@
         <v>28025080,1969,</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A472" s="1">
         <v>28025080</v>
       </c>
@@ -7200,7 +7201,7 @@
         <v>28025080,1970,</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A473" s="1">
         <v>28025080</v>
       </c>
@@ -7212,7 +7213,7 @@
         <v>28025080,1971,</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A474" s="1">
         <v>28025080</v>
       </c>
@@ -7224,7 +7225,7 @@
         <v>28025080,1972,</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A475" s="1">
         <v>28025080</v>
       </c>
@@ -7236,7 +7237,7 @@
         <v>28025080,1973,</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A476" s="1">
         <v>28025080</v>
       </c>
@@ -7248,7 +7249,7 @@
         <v>28025080,1974,</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A477" s="1">
         <v>28025080</v>
       </c>
@@ -7260,7 +7261,7 @@
         <v>28025080,1975,</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A478" s="1">
         <v>28025080</v>
       </c>
@@ -7272,7 +7273,7 @@
         <v>28025080,1976,</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A479" s="1">
         <v>28025080</v>
       </c>
@@ -7287,7 +7288,7 @@
         <v>28025080,1977,97.7</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A480" s="1">
         <v>28025080</v>
       </c>
@@ -7302,7 +7303,7 @@
         <v>28025080,1978,71.5</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A481" s="1">
         <v>28025080</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>28025080,1979,110.5</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A482" s="1">
         <v>28025080</v>
       </c>
@@ -7332,7 +7333,7 @@
         <v>28025080,1980,120.7</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A483" s="1">
         <v>28025080</v>
       </c>
@@ -7347,7 +7348,7 @@
         <v>28025080,1981,111.5</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A484" s="1">
         <v>28025080</v>
       </c>
@@ -7362,7 +7363,7 @@
         <v>28025080,1982,104.9</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A485" s="1">
         <v>28025080</v>
       </c>
@@ -7377,7 +7378,7 @@
         <v>28025080,1983,90.4</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A486" s="1">
         <v>28025080</v>
       </c>
@@ -7392,7 +7393,7 @@
         <v>28025080,1984,118.5</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A487" s="1">
         <v>28025080</v>
       </c>
@@ -7407,7 +7408,7 @@
         <v>28025080,1985,130.3</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A488" s="1">
         <v>28025080</v>
       </c>
@@ -7422,7 +7423,7 @@
         <v>28025080,1986,71.1</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A489" s="1">
         <v>28025080</v>
       </c>
@@ -7437,7 +7438,7 @@
         <v>28025080,1987,90.1</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A490" s="1">
         <v>28025080</v>
       </c>
@@ -7452,7 +7453,7 @@
         <v>28025080,1988,146.7</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A491" s="1">
         <v>28025080</v>
       </c>
@@ -7467,7 +7468,7 @@
         <v>28025080,1989,70.3</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A492" s="1">
         <v>28025080</v>
       </c>
@@ -7482,7 +7483,7 @@
         <v>28025080,1990,72.2</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A493" s="1">
         <v>28025080</v>
       </c>
@@ -7497,7 +7498,7 @@
         <v>28025080,1991,71.6</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A494" s="1">
         <v>28025080</v>
       </c>
@@ -7512,7 +7513,7 @@
         <v>28025080,1992,117</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A495" s="1">
         <v>28025080</v>
       </c>
@@ -7527,7 +7528,7 @@
         <v>28025080,1993,70</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A496" s="1">
         <v>28025080</v>
       </c>
@@ -7542,7 +7543,7 @@
         <v>28025080,1994,112.5</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="497" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A497" s="1">
         <v>28025080</v>
       </c>
@@ -7557,7 +7558,7 @@
         <v>28025080,1995,104</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="498" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A498" s="1">
         <v>28025080</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>28025080,1996,111</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="499" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A499" s="1">
         <v>28025080</v>
       </c>
@@ -7587,7 +7588,7 @@
         <v>28025080,1997,98.3</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="500" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A500" s="1">
         <v>28025080</v>
       </c>
@@ -7602,7 +7603,7 @@
         <v>28025080,1998,85.1</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="501" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A501" s="1">
         <v>28025080</v>
       </c>
@@ -7617,7 +7618,7 @@
         <v>28025080,1999,120</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="502" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A502" s="1">
         <v>28025080</v>
       </c>
@@ -7632,7 +7633,7 @@
         <v>28025080,2000,99</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="503" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A503" s="1">
         <v>28025080</v>
       </c>
@@ -7647,7 +7648,7 @@
         <v>28025080,2001,133</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="504" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A504" s="1">
         <v>28025080</v>
       </c>
@@ -7662,7 +7663,7 @@
         <v>28025080,2002,55</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="505" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A505" s="1">
         <v>28025080</v>
       </c>
@@ -7674,7 +7675,7 @@
         <v>28025080,2003,</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="506" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A506" s="1">
         <v>28025080</v>
       </c>
@@ -7689,7 +7690,7 @@
         <v>28025080,2004,85</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="507" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A507" s="1">
         <v>28025080</v>
       </c>
@@ -7704,7 +7705,7 @@
         <v>28025080,2005,104</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="508" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A508" s="1">
         <v>28025080</v>
       </c>
@@ -7719,7 +7720,7 @@
         <v>28025080,2006,72</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="509" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A509" s="1">
         <v>28025080</v>
       </c>
@@ -7734,7 +7735,7 @@
         <v>28025080,2007,110</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="510" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A510" s="1">
         <v>28025080</v>
       </c>
@@ -7749,7 +7750,7 @@
         <v>28025080,2008,80</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="511" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A511" s="1">
         <v>28025080</v>
       </c>
@@ -7764,7 +7765,7 @@
         <v>28025080,2009,85.1</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="512" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A512" s="1">
         <v>28025090</v>
       </c>
@@ -7776,7 +7777,7 @@
         <v>28025090,1959,</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="513" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A513" s="1">
         <v>28025090</v>
       </c>
@@ -7788,7 +7789,7 @@
         <v>28025090,1960,</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="514" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A514" s="1">
         <v>28025090</v>
       </c>
@@ -7800,7 +7801,7 @@
         <v>28025090,1961,</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="515" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A515" s="1">
         <v>28025090</v>
       </c>
@@ -7812,7 +7813,7 @@
         <v>28025090,1962,</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="516" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A516" s="1">
         <v>28025090</v>
       </c>
@@ -7824,7 +7825,7 @@
         <v>28025090,1963,</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="517" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A517" s="1">
         <v>28025090</v>
       </c>
@@ -7836,7 +7837,7 @@
         <v>28025090,1964,</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="518" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A518" s="1">
         <v>28025090</v>
       </c>
@@ -7848,7 +7849,7 @@
         <v>28025090,1965,</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="519" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A519" s="1">
         <v>28025090</v>
       </c>
@@ -7860,7 +7861,7 @@
         <v>28025090,1966,</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="520" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A520" s="1">
         <v>28025090</v>
       </c>
@@ -7872,7 +7873,7 @@
         <v>28025090,1967,</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="521" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A521" s="1">
         <v>28025090</v>
       </c>
@@ -7884,7 +7885,7 @@
         <v>28025090,1968,</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="522" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A522" s="1">
         <v>28025090</v>
       </c>
@@ -7896,7 +7897,7 @@
         <v>28025090,1969,</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="523" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A523" s="1">
         <v>28025090</v>
       </c>
@@ -7908,7 +7909,7 @@
         <v>28025090,1970,</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="524" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A524" s="1">
         <v>28025090</v>
       </c>
@@ -7920,7 +7921,7 @@
         <v>28025090,1971,</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="525" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A525" s="1">
         <v>28025090</v>
       </c>
@@ -7932,7 +7933,7 @@
         <v>28025090,1972,</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="526" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A526" s="1">
         <v>28025090</v>
       </c>
@@ -7944,7 +7945,7 @@
         <v>28025090,1973,</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="527" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A527" s="1">
         <v>28025090</v>
       </c>
@@ -7956,7 +7957,7 @@
         <v>28025090,1974,</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="528" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A528" s="1">
         <v>28025090</v>
       </c>
@@ -7968,7 +7969,7 @@
         <v>28025090,1975,</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="529" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A529" s="1">
         <v>28025090</v>
       </c>
@@ -7980,7 +7981,7 @@
         <v>28025090,1976,</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="530" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A530" s="1">
         <v>28025090</v>
       </c>
@@ -7992,7 +7993,7 @@
         <v>28025090,1977,</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="531" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A531" s="1">
         <v>28025090</v>
       </c>
@@ -8007,7 +8008,7 @@
         <v>28025090,1978,78</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="532" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A532" s="1">
         <v>28025090</v>
       </c>
@@ -8022,7 +8023,7 @@
         <v>28025090,1979,78</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="533" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A533" s="1">
         <v>28025090</v>
       </c>
@@ -8037,7 +8038,7 @@
         <v>28025090,1980,103.6</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="534" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A534" s="1">
         <v>28025090</v>
       </c>
@@ -8052,7 +8053,7 @@
         <v>28025090,1981,87.7</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="535" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A535" s="1">
         <v>28025090</v>
       </c>
@@ -8067,7 +8068,7 @@
         <v>28025090,1982,64</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="536" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A536" s="1">
         <v>28025090</v>
       </c>
@@ -8082,7 +8083,7 @@
         <v>28025090,1983,133.4</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="537" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A537" s="1">
         <v>28025090</v>
       </c>
@@ -8097,7 +8098,7 @@
         <v>28025090,1984,116.8</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="538" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A538" s="1">
         <v>28025090</v>
       </c>
@@ -8112,7 +8113,7 @@
         <v>28025090,1985,123.4</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="539" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A539" s="1">
         <v>28025090</v>
       </c>
@@ -8127,7 +8128,7 @@
         <v>28025090,1986,80.8</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="540" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A540" s="1">
         <v>28025090</v>
       </c>
@@ -8142,7 +8143,7 @@
         <v>28025090,1987,124.6</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="541" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A541" s="1">
         <v>28025090</v>
       </c>
@@ -8157,7 +8158,7 @@
         <v>28025090,1988,91.8</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="542" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A542" s="1">
         <v>28025090</v>
       </c>
@@ -8172,7 +8173,7 @@
         <v>28025090,1989,115.2</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="543" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A543" s="1">
         <v>28025090</v>
       </c>
@@ -8187,7 +8188,7 @@
         <v>28025090,1990,122</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="544" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A544" s="1">
         <v>28025090</v>
       </c>
@@ -8202,7 +8203,7 @@
         <v>28025090,1991,75</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="545" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A545" s="1">
         <v>28025090</v>
       </c>
@@ -8217,7 +8218,7 @@
         <v>28025090,1992,102</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="546" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A546" s="1">
         <v>28025090</v>
       </c>
@@ -8232,7 +8233,7 @@
         <v>28025090,1993,90</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="547" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A547" s="1">
         <v>28025090</v>
       </c>
@@ -8247,7 +8248,7 @@
         <v>28025090,1994,85</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="548" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A548" s="1">
         <v>28025090</v>
       </c>
@@ -8262,7 +8263,7 @@
         <v>28025090,1995,81</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="549" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A549" s="1">
         <v>28025090</v>
       </c>
@@ -8277,7 +8278,7 @@
         <v>28025090,1996,121.9</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="550" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A550" s="1">
         <v>28025090</v>
       </c>
@@ -8292,7 +8293,7 @@
         <v>28025090,1997,84</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="551" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A551" s="1">
         <v>28025090</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>28025090,1998,111</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="552" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A552" s="1">
         <v>28025090</v>
       </c>
@@ -8322,7 +8323,7 @@
         <v>28025090,1999,100</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="553" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A553" s="1">
         <v>28025090</v>
       </c>
@@ -8337,7 +8338,7 @@
         <v>28025090,2000,118</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="554" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A554" s="1">
         <v>28025090</v>
       </c>
@@ -8352,7 +8353,7 @@
         <v>28025090,2001,85.7</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="555" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A555" s="1">
         <v>28025090</v>
       </c>
@@ -8367,7 +8368,7 @@
         <v>28025090,2002,79</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="556" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A556" s="1">
         <v>28025090</v>
       </c>
@@ -8382,7 +8383,7 @@
         <v>28025090,2003,77</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="557" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A557" s="1">
         <v>28025090</v>
       </c>
@@ -8397,7 +8398,7 @@
         <v>28025090,2004,90</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="558" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A558" s="1">
         <v>28025090</v>
       </c>
@@ -8412,7 +8413,7 @@
         <v>28025090,2005,77</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="559" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A559" s="1">
         <v>28025090</v>
       </c>
@@ -8427,7 +8428,7 @@
         <v>28025090,2006,112</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="560" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A560" s="1">
         <v>28025090</v>
       </c>
@@ -8442,7 +8443,7 @@
         <v>28025090,2007,91</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="561" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A561" s="1">
         <v>28025090</v>
       </c>
@@ -8457,7 +8458,7 @@
         <v>28025090,2008,131</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="562" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A562" s="1">
         <v>28025090</v>
       </c>
@@ -8472,7 +8473,7 @@
         <v>28025090,2009,141</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="563" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A563" s="1">
         <v>28035040</v>
       </c>
@@ -8484,7 +8485,7 @@
         <v>28035040,1959,</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="564" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A564" s="1">
         <v>28035040</v>
       </c>
@@ -8496,7 +8497,7 @@
         <v>28035040,1960,</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="565" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A565" s="1">
         <v>28035040</v>
       </c>
@@ -8508,7 +8509,7 @@
         <v>28035040,1961,</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="566" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A566" s="1">
         <v>28035040</v>
       </c>
@@ -8520,7 +8521,7 @@
         <v>28035040,1962,</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="567" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A567" s="1">
         <v>28035040</v>
       </c>
@@ -8532,7 +8533,7 @@
         <v>28035040,1963,</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="568" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A568" s="1">
         <v>28035040</v>
       </c>
@@ -8544,7 +8545,7 @@
         <v>28035040,1964,</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="569" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A569" s="1">
         <v>28035040</v>
       </c>
@@ -8556,7 +8557,7 @@
         <v>28035040,1965,</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="570" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A570" s="1">
         <v>28035040</v>
       </c>
@@ -8568,7 +8569,7 @@
         <v>28035040,1966,</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="571" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A571" s="1">
         <v>28035040</v>
       </c>
@@ -8580,7 +8581,7 @@
         <v>28035040,1967,</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="572" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A572" s="1">
         <v>28035040</v>
       </c>
@@ -8592,7 +8593,7 @@
         <v>28035040,1968,</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="573" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A573" s="1">
         <v>28035040</v>
       </c>
@@ -8604,7 +8605,7 @@
         <v>28035040,1969,</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="574" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A574" s="1">
         <v>28035040</v>
       </c>
@@ -8616,7 +8617,7 @@
         <v>28035040,1970,</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="575" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A575" s="1">
         <v>28035040</v>
       </c>
@@ -8628,7 +8629,7 @@
         <v>28035040,1971,</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="576" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A576" s="1">
         <v>28035040</v>
       </c>
@@ -8643,7 +8644,7 @@
         <v>28035040,1972,75</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="577" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A577" s="1">
         <v>28035040</v>
       </c>
@@ -8658,7 +8659,7 @@
         <v>28035040,1973,52</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="578" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A578" s="1">
         <v>28035040</v>
       </c>
@@ -8673,7 +8674,7 @@
         <v>28035040,1974,65</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="579" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A579" s="1">
         <v>28035040</v>
       </c>
@@ -8688,7 +8689,7 @@
         <v>28035040,1975,73</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="580" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A580" s="1">
         <v>28035040</v>
       </c>
@@ -8703,7 +8704,7 @@
         <v>28035040,1976,67.5</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="581" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A581" s="1">
         <v>28035040</v>
       </c>
@@ -8718,7 +8719,7 @@
         <v>28035040,1977,28</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="582" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A582" s="1">
         <v>28035040</v>
       </c>
@@ -8733,7 +8734,7 @@
         <v>28035040,1978,99</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="583" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A583" s="1">
         <v>28035040</v>
       </c>
@@ -8748,7 +8749,7 @@
         <v>28035040,1979,121</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="584" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A584" s="1">
         <v>28035040</v>
       </c>
@@ -8763,7 +8764,7 @@
         <v>28035040,1980,72.4</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="585" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A585" s="1">
         <v>28035040</v>
       </c>
@@ -8778,7 +8779,7 @@
         <v>28035040,1981,96</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="586" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A586" s="1">
         <v>28035040</v>
       </c>
@@ -8793,7 +8794,7 @@
         <v>28035040,1982,105.5</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="587" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A587" s="1">
         <v>28035040</v>
       </c>
@@ -8808,7 +8809,7 @@
         <v>28035040,1983,56</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="588" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A588" s="1">
         <v>28035040</v>
       </c>
@@ -8823,7 +8824,7 @@
         <v>28035040,1984,90.1</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="589" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A589" s="1">
         <v>28035040</v>
       </c>
@@ -8838,7 +8839,7 @@
         <v>28035040,1985,114.4</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="590" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A590" s="1">
         <v>28035040</v>
       </c>
@@ -8853,7 +8854,7 @@
         <v>28035040,1986,103.7</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="591" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A591" s="1">
         <v>28035040</v>
       </c>
@@ -8868,7 +8869,7 @@
         <v>28035040,1987,91.1</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="592" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A592" s="1">
         <v>28035040</v>
       </c>
@@ -8883,7 +8884,7 @@
         <v>28035040,1988,135</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="593" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A593" s="1">
         <v>28035040</v>
       </c>
@@ -8898,7 +8899,7 @@
         <v>28035040,1989,90</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="594" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A594" s="1">
         <v>28035040</v>
       </c>
@@ -8913,7 +8914,7 @@
         <v>28035040,1990,84</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="595" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A595" s="1">
         <v>28035040</v>
       </c>
@@ -8928,7 +8929,7 @@
         <v>28035040,1991,84</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="596" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A596" s="1">
         <v>28035040</v>
       </c>
@@ -8943,7 +8944,7 @@
         <v>28035040,1992,83</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="597" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A597" s="1">
         <v>28035040</v>
       </c>
@@ -8958,7 +8959,7 @@
         <v>28035040,1993,83</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="598" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A598" s="1">
         <v>28035040</v>
       </c>
@@ -8970,7 +8971,7 @@
         <v>28035040,1994,</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="599" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A599" s="1">
         <v>28035040</v>
       </c>
@@ -8985,7 +8986,7 @@
         <v>28035040,1995,127</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="600" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A600" s="1">
         <v>28035040</v>
       </c>
@@ -9000,7 +9001,7 @@
         <v>28035040,1996,85.7</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="601" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A601" s="1">
         <v>28035040</v>
       </c>
@@ -9015,7 +9016,7 @@
         <v>28035040,1997,65</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="602" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A602" s="1">
         <v>28035040</v>
       </c>
@@ -9030,7 +9031,7 @@
         <v>28035040,1998,108</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="603" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A603" s="1">
         <v>28035040</v>
       </c>
@@ -9045,7 +9046,7 @@
         <v>28035040,1999,100</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="604" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A604" s="1">
         <v>28035040</v>
       </c>
@@ -9060,7 +9061,7 @@
         <v>28035040,2000,81.8</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="605" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A605" s="1">
         <v>28035040</v>
       </c>
@@ -9075,7 +9076,7 @@
         <v>28035040,2001,90</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="606" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A606" s="1">
         <v>28035040</v>
       </c>
@@ -9090,7 +9091,7 @@
         <v>28035040,2002,59</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="607" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A607" s="1">
         <v>28035040</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>28035040,2003,</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="608" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A608" s="1">
         <v>28035040</v>
       </c>
@@ -9117,7 +9118,7 @@
         <v>28035040,2004,85</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="609" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A609" s="1">
         <v>28035040</v>
       </c>
@@ -9132,7 +9133,7 @@
         <v>28035040,2005,104</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="610" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A610" s="1">
         <v>28035040</v>
       </c>
@@ -9147,7 +9148,7 @@
         <v>28035040,2006,104</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="611" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A611" s="1">
         <v>28035040</v>
       </c>
@@ -9162,7 +9163,7 @@
         <v>28035040,2007,101</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="612" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A612" s="1">
         <v>28035040</v>
       </c>
@@ -9177,7 +9178,7 @@
         <v>28035040,2008,96</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="613" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A613" s="1">
         <v>28035040</v>
       </c>
@@ -9192,7 +9193,7 @@
         <v>28035040,2009,84</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="614" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A614" s="1">
         <v>28040310</v>
       </c>
@@ -9204,7 +9205,7 @@
         <v>28040310,1959,</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="615" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A615" s="1">
         <v>28040310</v>
       </c>
@@ -9216,7 +9217,7 @@
         <v>28040310,1960,</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="616" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A616" s="1">
         <v>28040310</v>
       </c>
@@ -9228,7 +9229,7 @@
         <v>28040310,1961,</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="617" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A617" s="1">
         <v>28040310</v>
       </c>
@@ -9240,7 +9241,7 @@
         <v>28040310,1962,</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="618" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A618" s="1">
         <v>28040310</v>
       </c>
@@ -9252,7 +9253,7 @@
         <v>28040310,1963,</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="619" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A619" s="1">
         <v>28040310</v>
       </c>
@@ -9264,7 +9265,7 @@
         <v>28040310,1964,</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="620" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A620" s="1">
         <v>28040310</v>
       </c>
@@ -9276,7 +9277,7 @@
         <v>28040310,1965,</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="621" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A621" s="1">
         <v>28040310</v>
       </c>
@@ -9288,7 +9289,7 @@
         <v>28040310,1966,</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="622" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A622" s="1">
         <v>28040310</v>
       </c>
@@ -9300,7 +9301,7 @@
         <v>28040310,1967,</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="623" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A623" s="1">
         <v>28040310</v>
       </c>
@@ -9312,7 +9313,7 @@
         <v>28040310,1968,</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="624" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A624" s="1">
         <v>28040310</v>
       </c>
@@ -9324,7 +9325,7 @@
         <v>28040310,1969,</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="625" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A625" s="1">
         <v>28040310</v>
       </c>
@@ -9336,7 +9337,7 @@
         <v>28040310,1970,</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="626" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A626" s="1">
         <v>28040310</v>
       </c>
@@ -9348,7 +9349,7 @@
         <v>28040310,1971,</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="627" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A627" s="1">
         <v>28040310</v>
       </c>
@@ -9360,7 +9361,7 @@
         <v>28040310,1972,</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="628" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A628" s="1">
         <v>28040310</v>
       </c>
@@ -9372,7 +9373,7 @@
         <v>28040310,1973,</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="629" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A629" s="1">
         <v>28040310</v>
       </c>
@@ -9384,7 +9385,7 @@
         <v>28040310,1974,</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="630" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A630" s="1">
         <v>28040310</v>
       </c>
@@ -9396,7 +9397,7 @@
         <v>28040310,1975,</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="631" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A631" s="1">
         <v>28040310</v>
       </c>
@@ -9408,7 +9409,7 @@
         <v>28040310,1976,</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="632" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A632" s="1">
         <v>28040310</v>
       </c>
@@ -9423,7 +9424,7 @@
         <v>28040310,1977,76</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="633" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A633" s="1">
         <v>28040310</v>
       </c>
@@ -9435,7 +9436,7 @@
         <v>28040310,1978,</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="634" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A634" s="1">
         <v>28040310</v>
       </c>
@@ -9447,7 +9448,7 @@
         <v>28040310,1979,</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="635" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A635" s="1">
         <v>28040310</v>
       </c>
@@ -9459,7 +9460,7 @@
         <v>28040310,1980,</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="636" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A636" s="1">
         <v>28040310</v>
       </c>
@@ -9474,7 +9475,7 @@
         <v>28040310,1981,136</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="637" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A637" s="1">
         <v>28040310</v>
       </c>
@@ -9489,7 +9490,7 @@
         <v>28040310,1982,94</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="638" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A638" s="1">
         <v>28040310</v>
       </c>
@@ -9504,7 +9505,7 @@
         <v>28040310,1983,109</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="639" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A639" s="1">
         <v>28040310</v>
       </c>
@@ -9519,7 +9520,7 @@
         <v>28040310,1984,95</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="640" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A640" s="1">
         <v>28040310</v>
       </c>
@@ -9534,7 +9535,7 @@
         <v>28040310,1985,92</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="641" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A641" s="1">
         <v>28040310</v>
       </c>
@@ -9549,7 +9550,7 @@
         <v>28040310,1986,87</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="642" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A642" s="1">
         <v>28040310</v>
       </c>
@@ -9564,7 +9565,7 @@
         <v>28040310,1987,72</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="643" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A643" s="1">
         <v>28040310</v>
       </c>
@@ -9579,7 +9580,7 @@
         <v>28040310,1988,160</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="644" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A644" s="1">
         <v>28040310</v>
       </c>
@@ -9594,7 +9595,7 @@
         <v>28040310,1989,82</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="645" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A645" s="1">
         <v>28040310</v>
       </c>
@@ -9609,7 +9610,7 @@
         <v>28040310,1990,95</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="646" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A646" s="1">
         <v>28040310</v>
       </c>
@@ -9624,7 +9625,7 @@
         <v>28040310,1991,90</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="647" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A647" s="1">
         <v>28040310</v>
       </c>
@@ -9639,7 +9640,7 @@
         <v>28040310,1992,74</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="648" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A648" s="1">
         <v>28040310</v>
       </c>
@@ -9654,7 +9655,7 @@
         <v>28040310,1993,105</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="649" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A649" s="1">
         <v>28040310</v>
       </c>
@@ -9669,7 +9670,7 @@
         <v>28040310,1994,95</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="650" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A650" s="1">
         <v>28040310</v>
       </c>
@@ -9684,7 +9685,7 @@
         <v>28040310,1995,85</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="651" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A651" s="1">
         <v>28040310</v>
       </c>
@@ -9699,7 +9700,7 @@
         <v>28040310,1996,164</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="652" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A652" s="1">
         <v>28040310</v>
       </c>
@@ -9714,7 +9715,7 @@
         <v>28040310,1997,75</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="653" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A653" s="1">
         <v>28040310</v>
       </c>
@@ -9729,7 +9730,7 @@
         <v>28040310,1998,55</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="654" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A654" s="1">
         <v>28040310</v>
       </c>
@@ -9744,7 +9745,7 @@
         <v>28040310,1999,114</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="655" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A655" s="1">
         <v>28040310</v>
       </c>
@@ -9759,7 +9760,7 @@
         <v>28040310,2000,87</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="656" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A656" s="1">
         <v>28040310</v>
       </c>
@@ -9774,7 +9775,7 @@
         <v>28040310,2001,82</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="657" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A657" s="1">
         <v>28040310</v>
       </c>
@@ -9789,7 +9790,7 @@
         <v>28040310,2002,86</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="658" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A658" s="1">
         <v>28040310</v>
       </c>
@@ -9804,7 +9805,7 @@
         <v>28040310,2003,90</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="659" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A659" s="1">
         <v>28040310</v>
       </c>
@@ -9819,7 +9820,7 @@
         <v>28040310,2004,72</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="660" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A660" s="1">
         <v>28040310</v>
       </c>
@@ -9834,7 +9835,7 @@
         <v>28040310,2005,74</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="661" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A661" s="1">
         <v>28040310</v>
       </c>
@@ -9849,7 +9850,7 @@
         <v>28040310,2006,90</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="662" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A662" s="1">
         <v>28040310</v>
       </c>
@@ -9864,7 +9865,7 @@
         <v>28040310,2007,80</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="663" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A663" s="1">
         <v>28040310</v>
       </c>
@@ -9879,7 +9880,7 @@
         <v>28040310,2008,140</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="664" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A664" s="1">
         <v>28040310</v>
       </c>
@@ -9891,7 +9892,7 @@
         <v>28040310,2009,</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="665" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A665" s="1">
         <v>28040350</v>
       </c>
@@ -9903,7 +9904,7 @@
         <v>28040350,1959,</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="666" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A666" s="1">
         <v>28040350</v>
       </c>
@@ -9915,7 +9916,7 @@
         <v>28040350,1960,</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="667" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A667" s="1">
         <v>28040350</v>
       </c>
@@ -9927,7 +9928,7 @@
         <v>28040350,1961,</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="668" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A668" s="1">
         <v>28040350</v>
       </c>
@@ -9939,7 +9940,7 @@
         <v>28040350,1962,</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="669" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A669" s="1">
         <v>28040350</v>
       </c>
@@ -9951,7 +9952,7 @@
         <v>28040350,1963,</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="670" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A670" s="1">
         <v>28040350</v>
       </c>
@@ -9963,7 +9964,7 @@
         <v>28040350,1964,</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="671" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A671" s="1">
         <v>28040350</v>
       </c>
@@ -9975,7 +9976,7 @@
         <v>28040350,1965,</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="672" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A672" s="1">
         <v>28040350</v>
       </c>
@@ -9987,7 +9988,7 @@
         <v>28040350,1966,</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="673" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A673" s="1">
         <v>28040350</v>
       </c>
@@ -9999,7 +10000,7 @@
         <v>28040350,1967,</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="674" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A674" s="1">
         <v>28040350</v>
       </c>
@@ -10011,7 +10012,7 @@
         <v>28040350,1968,</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="675" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A675" s="1">
         <v>28040350</v>
       </c>
@@ -10023,7 +10024,7 @@
         <v>28040350,1969,</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="676" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A676" s="1">
         <v>28040350</v>
       </c>
@@ -10035,7 +10036,7 @@
         <v>28040350,1970,</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="677" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A677" s="1">
         <v>28040350</v>
       </c>
@@ -10047,7 +10048,7 @@
         <v>28040350,1971,</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="678" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A678" s="1">
         <v>28040350</v>
       </c>
@@ -10062,7 +10063,7 @@
         <v>28040350,1972,47</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="679" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A679" s="1">
         <v>28040350</v>
       </c>
@@ -10077,7 +10078,7 @@
         <v>28040350,1973,70</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="680" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A680" s="1">
         <v>28040350</v>
       </c>
@@ -10092,7 +10093,7 @@
         <v>28040350,1974,90</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="681" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A681" s="1">
         <v>28040350</v>
       </c>
@@ -10107,7 +10108,7 @@
         <v>28040350,1975,140</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="682" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A682" s="1">
         <v>28040350</v>
       </c>
@@ -10122,7 +10123,7 @@
         <v>28040350,1976,151</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="683" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A683" s="1">
         <v>28040350</v>
       </c>
@@ -10137,7 +10138,7 @@
         <v>28040350,1977,102</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="684" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A684" s="1">
         <v>28040350</v>
       </c>
@@ -10152,7 +10153,7 @@
         <v>28040350,1978,97</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="685" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A685" s="1">
         <v>28040350</v>
       </c>
@@ -10167,7 +10168,7 @@
         <v>28040350,1979,140</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="686" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A686" s="1">
         <v>28040350</v>
       </c>
@@ -10182,7 +10183,7 @@
         <v>28040350,1980,80</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="687" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A687" s="1">
         <v>28040350</v>
       </c>
@@ -10197,7 +10198,7 @@
         <v>28040350,1981,99</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="688" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A688" s="1">
         <v>28040350</v>
       </c>
@@ -10212,7 +10213,7 @@
         <v>28040350,1982,112</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="689" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A689" s="1">
         <v>28040350</v>
       </c>
@@ -10227,7 +10228,7 @@
         <v>28040350,1983,120</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="690" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A690" s="1">
         <v>28040350</v>
       </c>
@@ -10242,7 +10243,7 @@
         <v>28040350,1984,84</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="691" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A691" s="1">
         <v>28040350</v>
       </c>
@@ -10257,7 +10258,7 @@
         <v>28040350,1985,99.8</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="692" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A692" s="1">
         <v>28040350</v>
       </c>
@@ -10272,7 +10273,7 @@
         <v>28040350,1986,75.2</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="693" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A693" s="1">
         <v>28040350</v>
       </c>
@@ -10287,7 +10288,7 @@
         <v>28040350,1987,122.6</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="694" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A694" s="1">
         <v>28040350</v>
       </c>
@@ -10302,7 +10303,7 @@
         <v>28040350,1988,89.5</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="695" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A695" s="1">
         <v>28040350</v>
       </c>
@@ -10317,7 +10318,7 @@
         <v>28040350,1989,73.5</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="696" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A696" s="1">
         <v>28040350</v>
       </c>
@@ -10332,7 +10333,7 @@
         <v>28040350,1990,85.3</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="697" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A697" s="1">
         <v>28040350</v>
       </c>
@@ -10347,7 +10348,7 @@
         <v>28040350,1991,107.5</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="698" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A698" s="1">
         <v>28040350</v>
       </c>
@@ -10362,7 +10363,7 @@
         <v>28040350,1992,130</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="699" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A699" s="1">
         <v>28040350</v>
       </c>
@@ -10377,7 +10378,7 @@
         <v>28040350,1993,117.3</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="700" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A700" s="1">
         <v>28040350</v>
       </c>
@@ -10392,7 +10393,7 @@
         <v>28040350,1994,95</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="701" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A701" s="1">
         <v>28040350</v>
       </c>
@@ -10407,7 +10408,7 @@
         <v>28040350,1995,80.5</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="702" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A702" s="1">
         <v>28040350</v>
       </c>
@@ -10422,7 +10423,7 @@
         <v>28040350,1996,146.5</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="703" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A703" s="1">
         <v>28040350</v>
       </c>
@@ -10437,7 +10438,7 @@
         <v>28040350,1997,56.8</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="704" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A704" s="1">
         <v>28040350</v>
       </c>
@@ -10452,7 +10453,7 @@
         <v>28040350,1998,103</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="705" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A705" s="1">
         <v>28040350</v>
       </c>
@@ -10467,7 +10468,7 @@
         <v>28040350,1999,113.5</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="706" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A706" s="1">
         <v>28040350</v>
       </c>
@@ -10482,7 +10483,7 @@
         <v>28040350,2000,88.8</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="707" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A707" s="1">
         <v>28040350</v>
       </c>
@@ -10497,7 +10498,7 @@
         <v>28040350,2001,55.5</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="708" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A708" s="1">
         <v>28040350</v>
       </c>
@@ -10512,7 +10513,7 @@
         <v>28040350,2002,104.5</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="709" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A709" s="1">
         <v>28040350</v>
       </c>
@@ -10527,7 +10528,7 @@
         <v>28040350,2003,27.3</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="710" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A710" s="1">
         <v>28040350</v>
       </c>
@@ -10542,7 +10543,7 @@
         <v>28040350,2004,87.8</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="711" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A711" s="1">
         <v>28040350</v>
       </c>
@@ -10557,7 +10558,7 @@
         <v>28040350,2005,119</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="712" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A712" s="1">
         <v>28040350</v>
       </c>
@@ -10572,7 +10573,7 @@
         <v>28040350,2006,133.5</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="713" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A713" s="1">
         <v>28040350</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>28040350,2007,67.5</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="714" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A714" s="1">
         <v>28040350</v>
       </c>
@@ -10602,7 +10603,7 @@
         <v>28040350,2008,110.7</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.6">
+    <row r="715" spans="1:4" hidden="1" x14ac:dyDescent="0.6">
       <c r="A715" s="1">
         <v>28040350</v>
       </c>
@@ -11245,7 +11246,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D766" xr:uid="{6E7C4D4F-C4DE-4983-AADE-B1C1D9129ECF}"/>
+  <autoFilter ref="A1:D766" xr:uid="{6E7C4D4F-C4DE-4983-AADE-B1C1D9129ECF}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="28045040"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C766">
     <sortCondition ref="A2:A766"/>
     <sortCondition ref="B2:B766"/>
